--- a/Projeto - Organizador de Declaração de Imposto de Renda.xlsx
+++ b/Projeto - Organizador de Declaração de Imposto de Renda.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Dani\Desktop\Google estudantes\Semana 8\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Dani\Desktop\Santander e DIO - Excel e IA\Projeto DIO - IR\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BD5DC179-7B12-491B-8840-D829F2A14B2E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3C1A3154-4F00-432A-95CC-3817C143F8C4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{786D8B1A-58A1-4A0C-8F05-8267F18AEF09}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="2" xr2:uid="{786D8B1A-58A1-4A0C-8F05-8267F18AEF09}"/>
   </bookViews>
   <sheets>
     <sheet name="Titular" sheetId="2" r:id="rId1"/>
@@ -329,11 +329,11 @@
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="6">
     <numFmt numFmtId="44" formatCode="_-&quot;R$&quot;\ * #,##0.00_-;\-&quot;R$&quot;\ * #,##0.00_-;_-&quot;R$&quot;\ * &quot;-&quot;??_-;_-@_-"/>
-    <numFmt numFmtId="169" formatCode="000&quot;.&quot;000&quot;.&quot;000&quot;-&quot;00"/>
-    <numFmt numFmtId="170" formatCode="00&quot;.&quot;000&quot;-&quot;00"/>
-    <numFmt numFmtId="171" formatCode="&quot;(&quot;00&quot;)&quot;00000&quot;-&quot;0000"/>
-    <numFmt numFmtId="172" formatCode="&quot;R$&quot;\ #,##0.00"/>
-    <numFmt numFmtId="178" formatCode="mm/yyyy"/>
+    <numFmt numFmtId="164" formatCode="000&quot;.&quot;000&quot;.&quot;000&quot;-&quot;00"/>
+    <numFmt numFmtId="165" formatCode="00&quot;.&quot;000&quot;-&quot;00"/>
+    <numFmt numFmtId="166" formatCode="&quot;(&quot;00&quot;)&quot;00000&quot;-&quot;0000"/>
+    <numFmt numFmtId="167" formatCode="&quot;R$&quot;\ #,##0.00"/>
+    <numFmt numFmtId="168" formatCode="mm/yyyy"/>
   </numFmts>
   <fonts count="13" x14ac:knownFonts="1">
     <font>
@@ -531,7 +531,51 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="172" fontId="11" fillId="2" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="167" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="168" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="2" xfId="2" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="164" fontId="2" fillId="2" borderId="2" xfId="2" applyNumberFormat="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="165" fontId="2" fillId="2" borderId="2" xfId="2" applyNumberFormat="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="166" fontId="2" fillId="2" borderId="2" xfId="2" applyNumberFormat="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="2" xfId="4" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="2" xfId="2" applyFont="1" applyBorder="1" applyProtection="1">
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="167" fontId="8" fillId="2" borderId="2" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyProtection="1">
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="167" fontId="2" fillId="2" borderId="2" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyProtection="1">
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="167" fontId="11" fillId="2" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="2" borderId="0" xfId="2" applyFont="1" applyAlignment="1">
@@ -542,50 +586,6 @@
     </xf>
     <xf numFmtId="0" fontId="3" fillId="3" borderId="0" xfId="3" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="172" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="178" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="2" xfId="2" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="169" fontId="2" fillId="2" borderId="2" xfId="2" applyNumberFormat="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="170" fontId="2" fillId="2" borderId="2" xfId="2" applyNumberFormat="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="171" fontId="2" fillId="2" borderId="2" xfId="2" applyNumberFormat="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="2" xfId="4" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="2" xfId="2" applyFont="1" applyBorder="1" applyProtection="1">
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="172" fontId="8" fillId="2" borderId="2" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyProtection="1">
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="172" fontId="2" fillId="2" borderId="2" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyProtection="1">
-      <protection locked="0"/>
     </xf>
   </cellXfs>
   <cellStyles count="5">
@@ -604,25 +604,6 @@
         <u val="none"/>
         <vertAlign val="baseline"/>
         <sz val="11"/>
-        <name val="Segoe UI Light"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="0"/>
         <name val="Segoe UI Light"/>
         <family val="2"/>
         <scheme val="none"/>
@@ -665,6 +646,25 @@
         <u val="none"/>
         <vertAlign val="baseline"/>
         <sz val="11"/>
+        <name val="Segoe UI Light"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="0"/>
         <name val="Segoe UI Light"/>
         <family val="2"/>
         <scheme val="none"/>
@@ -2091,7 +2091,7 @@
               </a:gradFill>
               <a:latin typeface="Arial Black" panose="020B0A04020102020204" pitchFamily="34" charset="0"/>
             </a:rPr>
-            <a:t>H&amp;D </a:t>
+            <a:t>LION </a:t>
           </a:r>
           <a:r>
             <a:rPr lang="pt-BR" sz="2400" b="1" baseline="0">
@@ -2514,12 +2514,12 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{489CC418-E823-410F-9082-BA4E35434BA0}" name="Tabela2" displayName="Tabela2" ref="C8:E26" totalsRowShown="0" headerRowDxfId="1" dataDxfId="0">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{489CC418-E823-410F-9082-BA4E35434BA0}" name="Tabela2" displayName="Tabela2" ref="C8:E26" totalsRowShown="0" headerRowDxfId="4" dataDxfId="3">
   <autoFilter ref="C8:E26" xr:uid="{489CC418-E823-410F-9082-BA4E35434BA0}"/>
   <tableColumns count="3">
-    <tableColumn id="1" xr3:uid="{7E50D13C-9A03-4654-9A55-0CF1F9831D11}" name="DATA" dataDxfId="4"/>
-    <tableColumn id="2" xr3:uid="{25223D72-5091-42E4-8C09-48AC6DE517DC}" name="CATEGORIA" dataDxfId="3"/>
-    <tableColumn id="3" xr3:uid="{19BC7F5D-23A1-40C4-A493-29F7D5293E38}" name="VALOR" dataDxfId="2"/>
+    <tableColumn id="1" xr3:uid="{7E50D13C-9A03-4654-9A55-0CF1F9831D11}" name="DATA" dataDxfId="2"/>
+    <tableColumn id="2" xr3:uid="{25223D72-5091-42E4-8C09-48AC6DE517DC}" name="CATEGORIA" dataDxfId="1"/>
+    <tableColumn id="3" xr3:uid="{19BC7F5D-23A1-40C4-A493-29F7D5293E38}" name="VALOR" dataDxfId="0"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium6" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -2864,106 +2864,106 @@
       <c r="D4" s="6"/>
     </row>
     <row r="6" spans="3:4" ht="16.8" x14ac:dyDescent="0.4">
-      <c r="C6" s="18" t="s">
+      <c r="C6" s="14" t="s">
         <v>0</v>
       </c>
-      <c r="D6" s="19" t="s">
+      <c r="D6" s="15" t="s">
         <v>16</v>
       </c>
     </row>
     <row r="7" spans="3:4" ht="16.8" x14ac:dyDescent="0.4">
-      <c r="C7" s="18" t="s">
+      <c r="C7" s="14" t="s">
         <v>1</v>
       </c>
-      <c r="D7" s="20">
+      <c r="D7" s="16">
         <v>9876543210</v>
       </c>
     </row>
     <row r="8" spans="3:4" ht="16.8" x14ac:dyDescent="0.4">
-      <c r="C8" s="18" t="s">
+      <c r="C8" s="14" t="s">
         <v>2</v>
       </c>
-      <c r="D8" s="19">
+      <c r="D8" s="15">
         <v>123456789</v>
       </c>
     </row>
     <row r="9" spans="3:4" ht="16.8" x14ac:dyDescent="0.4">
-      <c r="C9" s="18" t="s">
+      <c r="C9" s="14" t="s">
         <v>7</v>
       </c>
-      <c r="D9" s="19" t="s">
+      <c r="D9" s="15" t="s">
         <v>20</v>
       </c>
     </row>
     <row r="10" spans="3:4" ht="16.8" x14ac:dyDescent="0.4">
-      <c r="C10" s="18" t="s">
+      <c r="C10" s="14" t="s">
         <v>3</v>
       </c>
-      <c r="D10" s="19" t="s">
+      <c r="D10" s="15" t="s">
         <v>19</v>
       </c>
     </row>
     <row r="11" spans="3:4" ht="16.8" x14ac:dyDescent="0.4">
-      <c r="C11" s="18" t="s">
+      <c r="C11" s="14" t="s">
         <v>4</v>
       </c>
-      <c r="D11" s="19" t="s">
+      <c r="D11" s="15" t="s">
         <v>18</v>
       </c>
     </row>
     <row r="12" spans="3:4" ht="16.8" x14ac:dyDescent="0.4">
-      <c r="C12" s="18" t="s">
+      <c r="C12" s="14" t="s">
         <v>5</v>
       </c>
-      <c r="D12" s="21">
+      <c r="D12" s="17">
         <v>4400000</v>
       </c>
     </row>
     <row r="13" spans="3:4" ht="16.8" x14ac:dyDescent="0.4">
-      <c r="C13" s="18" t="s">
+      <c r="C13" s="14" t="s">
         <v>6</v>
       </c>
-      <c r="D13" s="22">
+      <c r="D13" s="18">
         <v>87997302397</v>
       </c>
     </row>
     <row r="14" spans="3:4" ht="16.8" x14ac:dyDescent="0.4">
-      <c r="C14" s="18" t="s">
+      <c r="C14" s="14" t="s">
         <v>8</v>
       </c>
-      <c r="D14" s="22">
+      <c r="D14" s="18">
         <v>87997302397</v>
       </c>
     </row>
     <row r="15" spans="3:4" ht="16.8" x14ac:dyDescent="0.4">
-      <c r="C15" s="18" t="s">
+      <c r="C15" s="14" t="s">
         <v>9</v>
       </c>
-      <c r="D15" s="23" t="s">
+      <c r="D15" s="19" t="s">
         <v>17</v>
       </c>
     </row>
     <row r="16" spans="3:4" ht="16.8" x14ac:dyDescent="0.4">
-      <c r="C16" s="18" t="s">
+      <c r="C16" s="14" t="s">
         <v>10</v>
       </c>
-      <c r="D16" s="19" t="s">
+      <c r="D16" s="15" t="s">
         <v>15</v>
       </c>
     </row>
     <row r="17" spans="3:4" ht="16.8" x14ac:dyDescent="0.4">
-      <c r="C17" s="18" t="s">
+      <c r="C17" s="14" t="s">
         <v>11</v>
       </c>
-      <c r="D17" s="19" t="s">
+      <c r="D17" s="15" t="s">
         <v>15</v>
       </c>
     </row>
     <row r="18" spans="3:4" ht="16.8" x14ac:dyDescent="0.4">
-      <c r="C18" s="18" t="s">
+      <c r="C18" s="14" t="s">
         <v>12</v>
       </c>
-      <c r="D18" s="19" t="s">
+      <c r="D18" s="15" t="s">
         <v>15</v>
       </c>
     </row>
@@ -3014,11 +3014,11 @@
     </row>
     <row r="7" spans="1:4" s="7" customFormat="1" ht="16.8" x14ac:dyDescent="0.4">
       <c r="A7" s="1"/>
-      <c r="C7" s="10">
+      <c r="C7" s="23">
         <f>SUM(D11,D16,D21)</f>
         <v>900000</v>
       </c>
-      <c r="D7" s="11"/>
+      <c r="D7" s="24"/>
     </row>
     <row r="8" spans="1:4" s="7" customFormat="1" ht="16.8" x14ac:dyDescent="0.4">
       <c r="A8" s="1"/>
@@ -3036,7 +3036,7 @@
       <c r="C10" s="3" t="s">
         <v>23</v>
       </c>
-      <c r="D10" s="24" t="s">
+      <c r="D10" s="20" t="s">
         <v>29</v>
       </c>
     </row>
@@ -3044,7 +3044,7 @@
       <c r="C11" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="D11" s="25">
+      <c r="D11" s="21">
         <v>500000</v>
       </c>
     </row>
@@ -3052,7 +3052,7 @@
       <c r="C12" s="3" t="s">
         <v>25</v>
       </c>
-      <c r="D12" s="24" t="s">
+      <c r="D12" s="20" t="s">
         <v>26</v>
       </c>
     </row>
@@ -3070,7 +3070,7 @@
       <c r="C15" s="3" t="s">
         <v>23</v>
       </c>
-      <c r="D15" s="24" t="s">
+      <c r="D15" s="20" t="s">
         <v>32</v>
       </c>
     </row>
@@ -3078,7 +3078,7 @@
       <c r="C16" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="D16" s="25">
+      <c r="D16" s="21">
         <v>100000</v>
       </c>
     </row>
@@ -3086,7 +3086,7 @@
       <c r="C17" s="3" t="s">
         <v>25</v>
       </c>
-      <c r="D17" s="24" t="s">
+      <c r="D17" s="20" t="s">
         <v>81</v>
       </c>
     </row>
@@ -3104,7 +3104,7 @@
       <c r="C20" s="3" t="s">
         <v>23</v>
       </c>
-      <c r="D20" s="24" t="s">
+      <c r="D20" s="20" t="s">
         <v>38</v>
       </c>
     </row>
@@ -3112,7 +3112,7 @@
       <c r="C21" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="D21" s="26">
+      <c r="D21" s="22">
         <v>300000</v>
       </c>
     </row>
@@ -3120,7 +3120,7 @@
       <c r="C22" s="3" t="s">
         <v>25</v>
       </c>
-      <c r="D22" s="24" t="s">
+      <c r="D22" s="20" t="s">
         <v>82</v>
       </c>
     </row>
@@ -3173,186 +3173,186 @@
       <c r="E4" s="6"/>
     </row>
     <row r="7" spans="3:5" ht="16.8" x14ac:dyDescent="0.4">
-      <c r="C7" s="12" t="s">
+      <c r="C7" s="25" t="s">
         <v>89</v>
       </c>
-      <c r="D7" s="13"/>
-      <c r="E7" s="13"/>
+      <c r="D7" s="26"/>
+      <c r="E7" s="26"/>
     </row>
     <row r="8" spans="3:5" ht="16.8" x14ac:dyDescent="0.3">
-      <c r="C8" s="14" t="s">
+      <c r="C8" s="10" t="s">
         <v>86</v>
       </c>
-      <c r="D8" s="14" t="s">
+      <c r="D8" s="10" t="s">
         <v>87</v>
       </c>
-      <c r="E8" s="14" t="s">
+      <c r="E8" s="10" t="s">
         <v>88</v>
       </c>
     </row>
     <row r="9" spans="3:5" ht="16.8" x14ac:dyDescent="0.3">
-      <c r="C9" s="17">
+      <c r="C9" s="13">
         <v>46309</v>
       </c>
-      <c r="D9" s="15" t="s">
+      <c r="D9" s="11" t="s">
         <v>90</v>
       </c>
-      <c r="E9" s="16">
+      <c r="E9" s="12">
         <v>3000</v>
       </c>
     </row>
     <row r="10" spans="3:5" ht="16.8" x14ac:dyDescent="0.3">
-      <c r="C10" s="17">
+      <c r="C10" s="13">
         <v>46310</v>
       </c>
-      <c r="D10" s="15" t="s">
+      <c r="D10" s="11" t="s">
         <v>91</v>
       </c>
-      <c r="E10" s="15"/>
+      <c r="E10" s="11"/>
     </row>
     <row r="11" spans="3:5" ht="16.8" x14ac:dyDescent="0.3">
-      <c r="C11" s="17">
+      <c r="C11" s="13">
         <v>46311</v>
       </c>
-      <c r="D11" s="15" t="s">
+      <c r="D11" s="11" t="s">
         <v>90</v>
       </c>
-      <c r="E11" s="15"/>
+      <c r="E11" s="11"/>
     </row>
     <row r="12" spans="3:5" ht="16.8" x14ac:dyDescent="0.3">
-      <c r="C12" s="17">
+      <c r="C12" s="13">
         <v>46312</v>
       </c>
-      <c r="D12" s="15" t="s">
+      <c r="D12" s="11" t="s">
         <v>90</v>
       </c>
-      <c r="E12" s="15"/>
+      <c r="E12" s="11"/>
     </row>
     <row r="13" spans="3:5" ht="16.8" x14ac:dyDescent="0.3">
-      <c r="C13" s="17">
+      <c r="C13" s="13">
         <v>46313</v>
       </c>
-      <c r="D13" s="15" t="s">
+      <c r="D13" s="11" t="s">
         <v>90</v>
       </c>
-      <c r="E13" s="15"/>
+      <c r="E13" s="11"/>
     </row>
     <row r="14" spans="3:5" ht="16.8" x14ac:dyDescent="0.3">
-      <c r="C14" s="17">
+      <c r="C14" s="13">
         <v>46314</v>
       </c>
-      <c r="D14" s="15" t="s">
+      <c r="D14" s="11" t="s">
         <v>92</v>
       </c>
-      <c r="E14" s="15"/>
+      <c r="E14" s="11"/>
     </row>
     <row r="15" spans="3:5" ht="16.8" x14ac:dyDescent="0.3">
-      <c r="C15" s="17">
+      <c r="C15" s="13">
         <v>46315</v>
       </c>
-      <c r="D15" s="15" t="s">
+      <c r="D15" s="11" t="s">
         <v>90</v>
       </c>
-      <c r="E15" s="15"/>
+      <c r="E15" s="11"/>
     </row>
     <row r="16" spans="3:5" ht="16.8" x14ac:dyDescent="0.3">
-      <c r="C16" s="17">
+      <c r="C16" s="13">
         <v>46316</v>
       </c>
-      <c r="D16" s="15" t="s">
+      <c r="D16" s="11" t="s">
         <v>90</v>
       </c>
-      <c r="E16" s="15"/>
+      <c r="E16" s="11"/>
     </row>
     <row r="17" spans="3:5" ht="16.8" x14ac:dyDescent="0.3">
-      <c r="C17" s="17">
+      <c r="C17" s="13">
         <v>46317</v>
       </c>
-      <c r="D17" s="15" t="s">
+      <c r="D17" s="11" t="s">
         <v>90</v>
       </c>
-      <c r="E17" s="15"/>
+      <c r="E17" s="11"/>
     </row>
     <row r="18" spans="3:5" ht="16.8" x14ac:dyDescent="0.3">
-      <c r="C18" s="17">
+      <c r="C18" s="13">
         <v>46318</v>
       </c>
-      <c r="D18" s="15" t="s">
+      <c r="D18" s="11" t="s">
         <v>92</v>
       </c>
-      <c r="E18" s="15"/>
+      <c r="E18" s="11"/>
     </row>
     <row r="19" spans="3:5" ht="16.8" x14ac:dyDescent="0.3">
-      <c r="C19" s="17">
+      <c r="C19" s="13">
         <v>46319</v>
       </c>
-      <c r="D19" s="15" t="s">
+      <c r="D19" s="11" t="s">
         <v>90</v>
       </c>
-      <c r="E19" s="15"/>
+      <c r="E19" s="11"/>
     </row>
     <row r="20" spans="3:5" ht="16.8" x14ac:dyDescent="0.3">
-      <c r="C20" s="17">
+      <c r="C20" s="13">
         <v>46320</v>
       </c>
-      <c r="D20" s="15" t="s">
+      <c r="D20" s="11" t="s">
         <v>90</v>
       </c>
-      <c r="E20" s="15"/>
+      <c r="E20" s="11"/>
     </row>
     <row r="21" spans="3:5" ht="16.8" x14ac:dyDescent="0.3">
-      <c r="C21" s="17">
+      <c r="C21" s="13">
         <v>46321</v>
       </c>
-      <c r="D21" s="15" t="s">
+      <c r="D21" s="11" t="s">
         <v>91</v>
       </c>
-      <c r="E21" s="15"/>
+      <c r="E21" s="11"/>
     </row>
     <row r="22" spans="3:5" ht="16.8" x14ac:dyDescent="0.3">
-      <c r="C22" s="17">
+      <c r="C22" s="13">
         <v>46322</v>
       </c>
-      <c r="D22" s="15" t="s">
+      <c r="D22" s="11" t="s">
         <v>90</v>
       </c>
-      <c r="E22" s="15"/>
+      <c r="E22" s="11"/>
     </row>
     <row r="23" spans="3:5" ht="16.8" x14ac:dyDescent="0.3">
-      <c r="C23" s="17">
+      <c r="C23" s="13">
         <v>46323</v>
       </c>
-      <c r="D23" s="15" t="s">
+      <c r="D23" s="11" t="s">
         <v>91</v>
       </c>
-      <c r="E23" s="15"/>
+      <c r="E23" s="11"/>
     </row>
     <row r="24" spans="3:5" ht="16.8" x14ac:dyDescent="0.3">
-      <c r="C24" s="17">
+      <c r="C24" s="13">
         <v>46324</v>
       </c>
-      <c r="D24" s="15" t="s">
+      <c r="D24" s="11" t="s">
         <v>91</v>
       </c>
-      <c r="E24" s="15"/>
+      <c r="E24" s="11"/>
     </row>
     <row r="25" spans="3:5" ht="16.8" x14ac:dyDescent="0.3">
-      <c r="C25" s="17">
+      <c r="C25" s="13">
         <v>46325</v>
       </c>
-      <c r="D25" s="15" t="s">
+      <c r="D25" s="11" t="s">
         <v>90</v>
       </c>
-      <c r="E25" s="15"/>
+      <c r="E25" s="11"/>
     </row>
     <row r="26" spans="3:5" ht="16.8" x14ac:dyDescent="0.3">
-      <c r="C26" s="17">
+      <c r="C26" s="13">
         <v>46326</v>
       </c>
-      <c r="D26" s="15" t="s">
+      <c r="D26" s="11" t="s">
         <v>90</v>
       </c>
-      <c r="E26" s="15"/>
+      <c r="E26" s="11"/>
     </row>
   </sheetData>
   <mergeCells count="1">
